--- a/main/StructureDefinition-bc-location-bundle.xlsx
+++ b/main/StructureDefinition-bc-location-bundle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-30T21:39:06+00:00</t>
+    <t>2026-04-01T23:28:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -361,7 +361,7 @@
     <t>A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -2365,7 +2365,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="8" hidden="true">
+    <row r="8">
       <c r="A8" t="s" s="2">
         <v>121</v>
       </c>
@@ -3953,7 +3953,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="22" hidden="true">
+    <row r="22">
       <c r="A22" t="s" s="2">
         <v>187</v>
       </c>
@@ -4067,7 +4067,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="23" hidden="true">
+    <row r="23">
       <c r="A23" t="s" s="2">
         <v>191</v>
       </c>
@@ -4861,7 +4861,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="30" hidden="true">
+    <row r="30">
       <c r="A30" t="s" s="2">
         <v>213</v>
       </c>
@@ -7009,7 +7009,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="49" hidden="true">
+    <row r="49">
       <c r="A49" t="s" s="2">
         <v>265</v>
       </c>
@@ -7577,7 +7577,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="54" hidden="true">
+    <row r="54">
       <c r="A54" t="s" s="2">
         <v>271</v>
       </c>
@@ -7691,7 +7691,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="55" hidden="true">
+    <row r="55">
       <c r="A55" t="s" s="2">
         <v>272</v>
       </c>
@@ -8485,7 +8485,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="62" hidden="true">
+    <row r="62">
       <c r="A62" t="s" s="2">
         <v>283</v>
       </c>
@@ -10633,7 +10633,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="81" hidden="true">
+    <row r="81">
       <c r="A81" t="s" s="2">
         <v>302</v>
       </c>
@@ -11201,7 +11201,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="86" hidden="true">
+    <row r="86">
       <c r="A86" t="s" s="2">
         <v>308</v>
       </c>
@@ -11315,7 +11315,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="87" hidden="true">
+    <row r="87">
       <c r="A87" t="s" s="2">
         <v>309</v>
       </c>
@@ -12109,7 +12109,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="94" hidden="true">
+    <row r="94">
       <c r="A94" t="s" s="2">
         <v>320</v>
       </c>
@@ -14257,7 +14257,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="113" hidden="true">
+    <row r="113">
       <c r="A113" t="s" s="2">
         <v>339</v>
       </c>
@@ -14825,7 +14825,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="118" hidden="true">
+    <row r="118">
       <c r="A118" t="s" s="2">
         <v>345</v>
       </c>
@@ -14939,7 +14939,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="119" hidden="true">
+    <row r="119">
       <c r="A119" t="s" s="2">
         <v>346</v>
       </c>
@@ -15733,7 +15733,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="126" hidden="true">
+    <row r="126">
       <c r="A126" t="s" s="2">
         <v>357</v>
       </c>
@@ -17999,12 +17999,12 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:AN145">
-    <filterColumn colId="6">
+    <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
       </customFilters>
     </filterColumn>
-    <filterColumn colId="26">
+    <filterColumn colId="27">
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
